--- a/Results/Study 1/GoogLeNet/Confusion Matrices.xlsx
+++ b/Results/Study 1/GoogLeNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="C2">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C3">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 1/GoogLeNet/Confusion Matrices.xlsx
+++ b/Results/Study 1/GoogLeNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C2">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C3">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
